--- a/data/biomass/biomass_roots_v2.xlsx
+++ b/data/biomass/biomass_roots_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://texastechuniversity-my.sharepoint.com/personal/monikell_ttu_edu/Documents/0_sorted_files/research/mk/exp_02/data/biomass/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrkel\Documents\git\2025_g34p\data\biomass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1840" documentId="8_{F21C694C-6164-454A-875A-D2F7FD2B435B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B16C35A5-2793-461D-88D0-642A0CF48C66}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FED0ADE-5D19-4E69-942A-5073C24D4021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{7C2F5384-3529-46A3-A3B9-88FF292BE176}"/>
+    <workbookView xWindow="28680" yWindow="-135" windowWidth="29040" windowHeight="15720" xr2:uid="{7C2F5384-3529-46A3-A3B9-88FF292BE176}"/>
   </bookViews>
   <sheets>
     <sheet name="biomass_shoots" sheetId="1" r:id="rId1"/>
@@ -47,9 +47,6 @@
     <t>individual</t>
   </si>
   <si>
-    <t>biomass_roots</t>
-  </si>
-  <si>
     <t>notes</t>
   </si>
   <si>
@@ -78,6 +75,9 @@
   </si>
   <si>
     <t>roots</t>
+  </si>
+  <si>
+    <t>biomass_roots_g</t>
   </si>
 </sst>
 </file>
@@ -979,14 +979,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EFF3E9B-147D-4957-B386-0058A7C6B06B}">
   <dimension ref="A1:D383"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -994,15 +994,15 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>325</v>
@@ -1011,9 +1011,9 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>379</v>
@@ -1022,9 +1022,9 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>384</v>
@@ -1033,9 +1033,9 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>373</v>
@@ -1044,9 +1044,9 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>352</v>
@@ -1055,9 +1055,9 @@
         <v>5.9964000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>300</v>
@@ -1066,9 +1066,9 @@
         <v>1.9199999999999998E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>340</v>
@@ -1077,9 +1077,9 @@
         <v>11.41</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>344</v>
@@ -1088,9 +1088,9 @@
         <v>3.9546000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>377</v>
@@ -1099,9 +1099,9 @@
         <v>9.4500000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>355</v>
@@ -1110,9 +1110,9 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12">
         <v>354</v>
@@ -1121,9 +1121,9 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13">
         <v>374</v>
@@ -1132,9 +1132,9 @@
         <v>0.1739</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14">
         <v>308</v>
@@ -1143,9 +1143,9 @@
         <v>3.2000000000000002E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>315</v>
@@ -1154,9 +1154,9 @@
         <v>0.57079999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>376</v>
@@ -1165,9 +1165,9 @@
         <v>0.1221</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17">
         <v>347</v>
@@ -1176,9 +1176,9 @@
         <v>12.93</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18">
         <v>337</v>
@@ -1187,12 +1187,12 @@
         <v>18.95</v>
       </c>
       <c r="D18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19">
         <v>326</v>
@@ -1201,9 +1201,9 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20">
         <v>380</v>
@@ -1212,9 +1212,9 @@
         <v>2.3999999999999998E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21">
         <v>361</v>
@@ -1223,9 +1223,9 @@
         <v>0.13020000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22">
         <v>316</v>
@@ -1234,9 +1234,9 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23">
         <v>309</v>
@@ -1245,9 +1245,9 @@
         <v>0.5544</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24">
         <v>372</v>
@@ -1256,9 +1256,9 @@
         <v>8.6999999999999994E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25">
         <v>311</v>
@@ -1267,9 +1267,9 @@
         <v>3.0999999999999999E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26">
         <v>345</v>
@@ -1278,9 +1278,9 @@
         <v>12.083</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27">
         <v>357</v>
@@ -1289,9 +1289,9 @@
         <v>0.26090000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28">
         <v>353</v>
@@ -1300,9 +1300,9 @@
         <v>0.188</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29">
         <v>307</v>
@@ -1311,9 +1311,9 @@
         <v>0.81330000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30">
         <v>320</v>
@@ -1322,9 +1322,9 @@
         <v>6.7699999999999996E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31">
         <v>371</v>
@@ -1333,9 +1333,9 @@
         <v>0.95909999999999995</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32">
         <v>333</v>
@@ -1344,9 +1344,9 @@
         <v>10.82</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33">
         <v>383</v>
@@ -1355,9 +1355,9 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34">
         <v>330</v>
@@ -1366,12 +1366,12 @@
         <v>2.452</v>
       </c>
       <c r="D34" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35">
         <v>378</v>
@@ -1380,9 +1380,9 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36">
         <v>302</v>
@@ -1391,9 +1391,9 @@
         <v>0.20930000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B37">
         <v>336</v>
@@ -1402,9 +1402,9 @@
         <v>5.2186000000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B38">
         <v>359</v>
@@ -1413,9 +1413,9 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B39">
         <v>343</v>
@@ -1424,9 +1424,9 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B40">
         <v>370</v>
@@ -1435,9 +1435,9 @@
         <v>4.4699999999999997E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B41">
         <v>329</v>
@@ -1446,9 +1446,9 @@
         <v>9.2241</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B42">
         <v>351</v>
@@ -1457,9 +1457,9 @@
         <v>3.1030000000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B43">
         <v>365</v>
@@ -1468,9 +1468,9 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44">
         <v>317</v>
@@ -1479,9 +1479,9 @@
         <v>0.76149999999999995</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B45">
         <v>314</v>
@@ -1490,9 +1490,9 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B46">
         <v>381</v>
@@ -1501,9 +1501,9 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B47">
         <v>301</v>
@@ -1512,9 +1512,9 @@
         <v>0.3659</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B48">
         <v>310</v>
@@ -1523,9 +1523,9 @@
         <v>0.1111</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B49">
         <v>324</v>
@@ -1534,9 +1534,9 @@
         <v>2.7183000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B50">
         <v>334</v>
@@ -1545,9 +1545,9 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B51">
         <v>306</v>
@@ -1556,9 +1556,9 @@
         <v>6.9999999999999999E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B52">
         <v>319</v>
@@ -1567,9 +1567,9 @@
         <v>3.3399999999999999E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B53">
         <v>131</v>
@@ -1578,9 +1578,9 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B54">
         <v>360</v>
@@ -1589,9 +1589,9 @@
         <v>0.21190000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55">
         <v>382</v>
@@ -1600,9 +1600,9 @@
         <v>0.20030000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56">
         <v>363</v>
@@ -1611,9 +1611,9 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B57">
         <v>342</v>
@@ -1622,9 +1622,9 @@
         <v>3.8397000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B58">
         <v>367</v>
@@ -1633,9 +1633,9 @@
         <v>4.6100000000000002E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B59">
         <v>321</v>
@@ -1644,9 +1644,9 @@
         <v>5.7435</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B60">
         <v>369</v>
@@ -1655,9 +1655,9 @@
         <v>0.2112</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B61">
         <v>313</v>
@@ -1666,9 +1666,9 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B62">
         <v>339</v>
@@ -1677,9 +1677,9 @@
         <v>7.9466000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B63">
         <v>322</v>
@@ -1688,9 +1688,9 @@
         <v>1.5397000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B64">
         <v>348</v>
@@ -1699,9 +1699,9 @@
         <v>8.9600000000000009</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B65">
         <v>323</v>
@@ -1710,9 +1710,9 @@
         <v>3.8660000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B66">
         <v>341</v>
@@ -1721,9 +1721,9 @@
         <v>7.3087</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B67">
         <v>332</v>
@@ -1732,9 +1732,9 @@
         <v>8.7927999999999997</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68">
         <v>318</v>
@@ -1743,9 +1743,9 @@
         <v>5.8799999999999998E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B69">
         <v>331</v>
@@ -1754,12 +1754,12 @@
         <v>14.82</v>
       </c>
       <c r="D69" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B70">
         <v>366</v>
@@ -1768,9 +1768,9 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B71">
         <v>328</v>
@@ -1779,9 +1779,9 @@
         <v>4.3109999999999999</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B72">
         <v>338</v>
@@ -1790,9 +1790,9 @@
         <v>3.2391999999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B73">
         <v>335</v>
@@ -1801,9 +1801,9 @@
         <v>2.9923000000000002</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74">
         <v>364</v>
@@ -1812,9 +1812,9 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B75">
         <v>304</v>
@@ -1823,9 +1823,9 @@
         <v>7.2900000000000006E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B76">
         <v>303</v>
@@ -1834,9 +1834,9 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B77">
         <v>349</v>
@@ -1845,9 +1845,9 @@
         <v>9.7809000000000008</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B78">
         <v>312</v>
@@ -1856,9 +1856,9 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B79">
         <v>350</v>
@@ -1867,12 +1867,12 @@
         <v>4.6802999999999999</v>
       </c>
       <c r="D79" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B80">
         <v>368</v>
@@ -1881,9 +1881,9 @@
         <v>3.0300000000000001E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B81">
         <v>346</v>
@@ -1892,9 +1892,9 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B82">
         <v>358</v>
@@ -1903,9 +1903,9 @@
         <v>0.2324</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B83">
         <v>327</v>
@@ -1914,9 +1914,9 @@
         <v>2.3029000000000002</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B84">
         <v>305</v>
@@ -1925,9 +1925,9 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B85">
         <v>212</v>
@@ -1936,9 +1936,9 @@
         <v>6.5273000000000003</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B86">
         <v>218</v>
@@ -1947,9 +1947,9 @@
         <v>1.9473</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B87">
         <v>281</v>
@@ -1958,12 +1958,12 @@
         <v>19.040199999999999</v>
       </c>
       <c r="D87" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B88">
         <v>241</v>
@@ -1972,9 +1972,9 @@
         <v>0.16489999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B89">
         <v>245</v>
@@ -1983,9 +1983,9 @@
         <v>1.6765000000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B90">
         <v>232</v>
@@ -1994,9 +1994,9 @@
         <v>0.1454</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B91">
         <v>230</v>
@@ -2005,9 +2005,9 @@
         <v>0.24160000000000001</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B92">
         <v>295</v>
@@ -2016,9 +2016,9 @@
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B93">
         <v>236</v>
@@ -2027,9 +2027,9 @@
         <v>1.41E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B94">
         <v>231</v>
@@ -2038,9 +2038,9 @@
         <v>0.33479999999999999</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B95">
         <v>292</v>
@@ -2049,9 +2049,9 @@
         <v>1.77E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B96">
         <v>287</v>
@@ -2060,9 +2060,9 @@
         <v>4.2519</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B97">
         <v>251</v>
@@ -2071,9 +2071,9 @@
         <v>2.4659</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B98">
         <v>289</v>
@@ -2082,12 +2082,12 @@
         <v>1E-4</v>
       </c>
       <c r="D98" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B99">
         <v>285</v>
@@ -2096,9 +2096,9 @@
         <v>7.4405999999999999</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B100">
         <v>296</v>
@@ -2107,9 +2107,9 @@
         <v>5.8900000000000001E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B101">
         <v>243</v>
@@ -2118,9 +2118,9 @@
         <v>1.3988</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B102">
         <v>209</v>
@@ -2129,9 +2129,9 @@
         <v>12.2828</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B103">
         <v>246</v>
@@ -2140,9 +2140,9 @@
         <v>0.43059999999999998</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B104">
         <v>219</v>
@@ -2151,9 +2151,9 @@
         <v>7.74</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B105">
         <v>222</v>
@@ -2162,9 +2162,9 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B106">
         <v>267</v>
@@ -2173,9 +2173,9 @@
         <v>13.87</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B107">
         <v>221</v>
@@ -2184,9 +2184,9 @@
         <v>7.51</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B108">
         <v>294</v>
@@ -2195,9 +2195,9 @@
         <v>0.33079999999999998</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B109">
         <v>200</v>
@@ -2206,9 +2206,9 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B110">
         <v>276</v>
@@ -2217,9 +2217,9 @@
         <v>7.26</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B111">
         <v>225</v>
@@ -2228,9 +2228,9 @@
         <v>0.1804</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B112">
         <v>272</v>
@@ -2239,9 +2239,9 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B113">
         <v>242</v>
@@ -2250,9 +2250,9 @@
         <v>2.1700000000000001E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B114">
         <v>280</v>
@@ -2261,9 +2261,9 @@
         <v>6.26</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B115">
         <v>282</v>
@@ -2272,9 +2272,9 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B116">
         <v>227</v>
@@ -2283,9 +2283,9 @@
         <v>1.5508999999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B117">
         <v>204</v>
@@ -2294,9 +2294,9 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B118">
         <v>273</v>
@@ -2305,9 +2305,9 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B119">
         <v>284</v>
@@ -2316,9 +2316,9 @@
         <v>8.4553999999999991</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B120">
         <v>210</v>
@@ -2327,9 +2327,9 @@
         <v>1.1722999999999999</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B121">
         <v>266</v>
@@ -2338,9 +2338,9 @@
         <v>1.6456999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B122">
         <v>240</v>
@@ -2349,9 +2349,9 @@
         <v>0.1991</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B123">
         <v>277</v>
@@ -2360,9 +2360,9 @@
         <v>6.1314000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B124">
         <v>255</v>
@@ -2371,9 +2371,9 @@
         <v>0.52800000000000002</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B125">
         <v>265</v>
@@ -2382,12 +2382,12 @@
         <v>17.23</v>
       </c>
       <c r="D125" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B126">
         <v>290</v>
@@ -2396,9 +2396,9 @@
         <v>2.7000000000000001E-3</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B127">
         <v>223</v>
@@ -2407,9 +2407,9 @@
         <v>3.3591000000000002</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B128">
         <v>233</v>
@@ -2418,9 +2418,9 @@
         <v>0.4622</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B129">
         <v>254</v>
@@ -2429,9 +2429,9 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B130">
         <v>278</v>
@@ -2440,9 +2440,9 @@
         <v>3.8485</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B131">
         <v>270</v>
@@ -2451,9 +2451,9 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B132">
         <v>247</v>
@@ -2462,9 +2462,9 @@
         <v>0.57899999999999996</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B133">
         <v>214</v>
@@ -2473,9 +2473,9 @@
         <v>3.6278000000000001</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B134">
         <v>274</v>
@@ -2484,9 +2484,9 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B135">
         <v>206</v>
@@ -2495,9 +2495,9 @@
         <v>3.0255000000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B136">
         <v>215</v>
@@ -2506,9 +2506,9 @@
         <v>2.9312999999999998</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B137">
         <v>293</v>
@@ -2517,9 +2517,9 @@
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B138">
         <v>229</v>
@@ -2528,9 +2528,9 @@
         <v>2.9624999999999999</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B139">
         <v>268</v>
@@ -2539,9 +2539,9 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B140">
         <v>213</v>
@@ -2550,9 +2550,9 @@
         <v>8.35</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B141">
         <v>271</v>
@@ -2561,9 +2561,9 @@
         <v>3.2172999999999998</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B142">
         <v>235</v>
@@ -2572,9 +2572,9 @@
         <v>2.7646999999999999</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B143">
         <v>275</v>
@@ -2583,9 +2583,9 @@
         <v>8.2899999999999991</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B144">
         <v>217</v>
@@ -2594,9 +2594,9 @@
         <v>2.9773999999999998</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B145">
         <v>279</v>
@@ -2605,9 +2605,9 @@
         <v>4.7141999999999999</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B146">
         <v>263</v>
@@ -2616,9 +2616,9 @@
         <v>1.1245000000000001</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B147">
         <v>259</v>
@@ -2627,9 +2627,9 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B148">
         <v>211</v>
@@ -2638,9 +2638,9 @@
         <v>8.5299999999999994</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B149">
         <v>202</v>
@@ -2649,9 +2649,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B150">
         <v>238</v>
@@ -2660,9 +2660,9 @@
         <v>0.35010000000000002</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B151">
         <v>234</v>
@@ -2671,9 +2671,9 @@
         <v>3.1699999999999999E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B152">
         <v>237</v>
@@ -2682,9 +2682,9 @@
         <v>1.0660000000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B153">
         <v>260</v>
@@ -2693,9 +2693,9 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B154">
         <v>220</v>
@@ -2704,9 +2704,9 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B155">
         <v>299</v>
@@ -2715,9 +2715,9 @@
         <v>2.0160999999999998</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B156">
         <v>207</v>
@@ -2726,9 +2726,9 @@
         <v>10.18</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B157">
         <v>203</v>
@@ -2737,9 +2737,9 @@
         <v>9.1892999999999994</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B158">
         <v>269</v>
@@ -2748,9 +2748,9 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B159">
         <v>244</v>
@@ -2759,9 +2759,9 @@
         <v>0.20030000000000001</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B160">
         <v>248</v>
@@ -2770,9 +2770,9 @@
         <v>4.07E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B161">
         <v>216</v>
@@ -2781,9 +2781,9 @@
         <v>4.4736000000000002</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B162">
         <v>283</v>
@@ -2792,9 +2792,9 @@
         <v>14.484400000000001</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B163">
         <v>256</v>
@@ -2803,9 +2803,9 @@
         <v>0.62270000000000003</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B164">
         <v>224</v>
@@ -2814,9 +2814,9 @@
         <v>1.8305</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B165">
         <v>258</v>
@@ -2825,9 +2825,9 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B166">
         <v>201</v>
@@ -2836,9 +2836,9 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B167">
         <v>239</v>
@@ -2847,9 +2847,9 @@
         <v>0.1784</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B168">
         <v>257</v>
@@ -2858,9 +2858,9 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B169">
         <v>261</v>
@@ -2869,9 +2869,9 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B170">
         <v>249</v>
@@ -2880,9 +2880,9 @@
         <v>0.1479</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B171">
         <v>226</v>
@@ -2891,9 +2891,9 @@
         <v>0.23499999999999999</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B172">
         <v>291</v>
@@ -2902,9 +2902,9 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B173">
         <v>228</v>
@@ -2913,9 +2913,9 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B174">
         <v>205</v>
@@ -2924,9 +2924,9 @@
         <v>6.2024999999999997</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B175">
         <v>262</v>
@@ -2935,9 +2935,9 @@
         <v>1.2383999999999999</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B176">
         <v>252</v>
@@ -2946,9 +2946,9 @@
         <v>0.16250000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B177">
         <v>253</v>
@@ -2957,9 +2957,9 @@
         <v>0.63549999999999995</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B178">
         <v>286</v>
@@ -2968,9 +2968,9 @@
         <v>2.9922</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B179">
         <v>158</v>
@@ -2979,9 +2979,9 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B180">
         <v>144</v>
@@ -2990,9 +2990,9 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B181">
         <v>145</v>
@@ -3001,12 +3001,12 @@
         <v>16.2</v>
       </c>
       <c r="D181" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B182">
         <v>120</v>
@@ -3015,9 +3015,9 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B183">
         <v>159</v>
@@ -3026,9 +3026,9 @@
         <v>3.9405999999999999</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B184" s="5">
         <v>195</v>
@@ -3037,9 +3037,9 @@
         <v>4.2420999999999998</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B185">
         <v>118</v>
@@ -3048,9 +3048,9 @@
         <v>1.4172</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B186">
         <v>127</v>
@@ -3059,9 +3059,9 @@
         <v>0.22159999999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B187">
         <v>163</v>
@@ -3070,9 +3070,9 @@
         <v>1.385</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B188">
         <v>123</v>
@@ -3081,9 +3081,9 @@
         <v>4.6631999999999998</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B189">
         <v>137</v>
@@ -3092,9 +3092,9 @@
         <v>6.9008000000000003</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B190">
         <v>132</v>
@@ -3103,9 +3103,9 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B191">
         <v>101</v>
@@ -3114,9 +3114,9 @@
         <v>3.1282999999999999</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B192">
         <v>177</v>
@@ -3125,9 +3125,9 @@
         <v>0.22239999999999999</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B193">
         <v>176</v>
@@ -3136,9 +3136,9 @@
         <v>0.23549999999999999</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B194">
         <v>106</v>
@@ -3147,9 +3147,9 @@
         <v>6.5100000000000005E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B195">
         <v>157</v>
@@ -3158,9 +3158,9 @@
         <v>5.1254999999999997</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B196">
         <v>147</v>
@@ -3169,9 +3169,9 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B197">
         <v>164</v>
@@ -3180,9 +3180,9 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B198">
         <v>124</v>
@@ -3191,9 +3191,9 @@
         <v>0.36770000000000003</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B199">
         <v>138</v>
@@ -3202,9 +3202,9 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B200">
         <v>170</v>
@@ -3213,9 +3213,9 @@
         <v>3.0300000000000001E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B201">
         <v>191</v>
@@ -3224,9 +3224,9 @@
         <v>0.16270000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B202">
         <v>162</v>
@@ -3235,9 +3235,9 @@
         <v>8.9800000000000005E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B203">
         <v>156</v>
@@ -3246,9 +3246,9 @@
         <v>5.1199000000000003</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B204">
         <v>139</v>
@@ -3257,9 +3257,9 @@
         <v>8.44</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B205">
         <v>125</v>
@@ -3268,9 +3268,9 @@
         <v>1.4272</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B206">
         <v>198</v>
@@ -3279,9 +3279,9 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B207">
         <v>105</v>
@@ -3290,9 +3290,9 @@
         <v>0.17660000000000001</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B208">
         <v>121</v>
@@ -3301,9 +3301,9 @@
         <v>0.42120000000000002</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B209">
         <v>192</v>
@@ -3312,9 +3312,9 @@
         <v>0.20680000000000001</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B210">
         <v>114</v>
@@ -3323,9 +3323,9 @@
         <v>8.43E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B211">
         <v>142</v>
@@ -3334,9 +3334,9 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B212">
         <v>148</v>
@@ -3345,9 +3345,9 @@
         <v>5.4295999999999998</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B213">
         <v>183</v>
@@ -3356,9 +3356,9 @@
         <v>0.1285</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B214">
         <v>196</v>
@@ -3367,9 +3367,9 @@
         <v>2.6682999999999999</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B215">
         <v>108</v>
@@ -3378,9 +3378,9 @@
         <v>0.99070000000000003</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B216">
         <v>102</v>
@@ -3389,9 +3389,9 @@
         <v>0.6774</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B217">
         <v>155</v>
@@ -3400,12 +3400,12 @@
         <v>9.7799999999999994</v>
       </c>
       <c r="D217" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B218">
         <v>143</v>
@@ -3414,9 +3414,9 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B219">
         <v>149</v>
@@ -3425,9 +3425,9 @@
         <v>12.52</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B220">
         <v>179</v>
@@ -3436,9 +3436,9 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B221">
         <v>146</v>
@@ -3447,9 +3447,9 @@
         <v>0.58730000000000004</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B222">
         <v>140</v>
@@ -3458,9 +3458,9 @@
         <v>3.1204000000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B223">
         <v>194</v>
@@ -3469,9 +3469,9 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B224">
         <v>134</v>
@@ -3480,9 +3480,9 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B225">
         <v>151</v>
@@ -3491,12 +3491,12 @@
         <v>3.38</v>
       </c>
       <c r="D225" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B226">
         <v>128</v>
@@ -3505,9 +3505,9 @@
         <v>0.33839999999999998</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B227">
         <v>107</v>
@@ -3516,9 +3516,9 @@
         <v>2.0232000000000001</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B228">
         <v>111</v>
@@ -3527,9 +3527,9 @@
         <v>0.39650000000000002</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B229">
         <v>122</v>
@@ -3538,9 +3538,9 @@
         <v>0.14349999999999999</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B230">
         <v>161</v>
@@ -3549,9 +3549,9 @@
         <v>0.23380000000000001</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B231">
         <v>172</v>
@@ -3560,9 +3560,9 @@
         <v>0.2737</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B232">
         <v>182</v>
@@ -3571,9 +3571,9 @@
         <v>0.4017</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B233">
         <v>136</v>
@@ -3582,9 +3582,9 @@
         <v>2.2195999999999998</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B234">
         <v>103</v>
@@ -3593,9 +3593,9 @@
         <v>2.5499999999999998E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B235">
         <v>100</v>
@@ -3604,9 +3604,9 @@
         <v>0.1452</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B236">
         <v>116</v>
@@ -3615,9 +3615,9 @@
         <v>0.1605</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B237">
         <v>190</v>
@@ -3626,9 +3626,9 @@
         <v>0.27410000000000001</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B238">
         <v>133</v>
@@ -3637,9 +3637,9 @@
         <v>4.7899000000000003</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B239">
         <v>181</v>
@@ -3648,9 +3648,9 @@
         <v>1.0054000000000001</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B240">
         <v>180</v>
@@ -3659,9 +3659,9 @@
         <v>0.12130000000000001</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B241">
         <v>160</v>
@@ -3670,9 +3670,9 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B242">
         <v>126</v>
@@ -3681,9 +3681,9 @@
         <v>0.8548</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B243">
         <v>168</v>
@@ -3692,9 +3692,9 @@
         <v>0.36930000000000002</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B244">
         <v>186</v>
@@ -3703,9 +3703,9 @@
         <v>2.41E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B245">
         <v>197</v>
@@ -3714,9 +3714,9 @@
         <v>4.2591000000000001</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B246">
         <v>193</v>
@@ -3725,9 +3725,9 @@
         <v>3.6554000000000002</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B247">
         <v>110</v>
@@ -3736,9 +3736,9 @@
         <v>1.0396000000000001</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B248">
         <v>175</v>
@@ -3747,9 +3747,9 @@
         <v>5.6899999999999999E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B249">
         <v>169</v>
@@ -3758,9 +3758,9 @@
         <v>0.28260000000000002</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B250">
         <v>113</v>
@@ -3769,9 +3769,9 @@
         <v>0.58299999999999996</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B251">
         <v>171</v>
@@ -3780,9 +3780,9 @@
         <v>4.0148999999999999</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B252">
         <v>150</v>
@@ -3791,9 +3791,9 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B253">
         <v>188</v>
@@ -3802,9 +3802,9 @@
         <v>9.4200000000000006E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B254">
         <v>112</v>
@@ -3813,9 +3813,9 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B255">
         <v>129</v>
@@ -3824,9 +3824,9 @@
         <v>4.2187000000000001</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B256">
         <v>109</v>
@@ -3835,9 +3835,9 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B257">
         <v>141</v>
@@ -3846,9 +3846,9 @@
         <v>4.5523999999999996</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B258">
         <v>152</v>
@@ -3857,9 +3857,9 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B259">
         <v>185</v>
@@ -3868,9 +3868,9 @@
         <v>2.4899999999999999E-2</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B260">
         <v>130</v>
@@ -3879,9 +3879,9 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B261">
         <v>165</v>
@@ -3890,9 +3890,9 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B262">
         <v>174</v>
@@ -3901,9 +3901,9 @@
         <v>0.49330000000000002</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B263">
         <v>199</v>
@@ -3912,9 +3912,9 @@
         <v>0.82469999999999999</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B264">
         <v>189</v>
@@ -3923,9 +3923,9 @@
         <v>1.2415</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B265">
         <v>154</v>
@@ -3934,9 +3934,9 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B266">
         <v>104</v>
@@ -3945,9 +3945,9 @@
         <v>0.3236</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B267">
         <v>173</v>
@@ -3956,9 +3956,9 @@
         <v>1.6073</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B268">
         <v>184</v>
@@ -3967,9 +3967,9 @@
         <v>0.42420000000000002</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B269">
         <v>135</v>
@@ -3978,9 +3978,9 @@
         <v>5.46</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B270">
         <v>178</v>
@@ -3989,9 +3989,9 @@
         <v>9.8299999999999998E-2</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B271">
         <v>166</v>
@@ -4000,9 +4000,9 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B272">
         <v>167</v>
@@ -4011,9 +4011,9 @@
         <v>0.2152</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B273">
         <v>115</v>
@@ -4022,9 +4022,9 @@
         <v>7.7939999999999996</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B274">
         <v>153</v>
@@ -4033,9 +4033,9 @@
         <v>3.1655000000000002</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B275">
         <v>187</v>
@@ -4044,9 +4044,9 @@
         <v>3.3147000000000002</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B276">
         <v>117</v>
@@ -4055,9 +4055,9 @@
         <v>1.1785000000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B277">
         <v>88</v>
@@ -4066,9 +4066,9 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B278">
         <v>92</v>
@@ -4077,9 +4077,9 @@
         <v>11.005100000000001</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B279">
         <v>70</v>
@@ -4088,9 +4088,9 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B280">
         <v>36</v>
@@ -4099,9 +4099,9 @@
         <v>0.1651</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B281">
         <v>22</v>
@@ -4110,9 +4110,9 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B282">
         <v>23</v>
@@ -4121,9 +4121,9 @@
         <v>3.4895</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B283">
         <v>74</v>
@@ -4132,9 +4132,9 @@
         <v>2.3365999999999998</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B284">
         <v>4</v>
@@ -4143,9 +4143,9 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B285">
         <v>51</v>
@@ -4154,9 +4154,9 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B286">
         <v>73</v>
@@ -4165,9 +4165,9 @@
         <v>13.717000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B287">
         <v>75</v>
@@ -4176,9 +4176,9 @@
         <v>9.48</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B288">
         <v>13</v>
@@ -4187,9 +4187,9 @@
         <v>6.6365999999999996</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B289">
         <v>85</v>
@@ -4198,9 +4198,9 @@
         <v>6.8446999999999996</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B290">
         <v>34</v>
@@ -4209,9 +4209,9 @@
         <v>0.2462</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B291">
         <v>68</v>
@@ -4220,9 +4220,9 @@
         <v>4.9740000000000002</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B292">
         <v>31</v>
@@ -4231,9 +4231,9 @@
         <v>3.1718999999999999</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B293">
         <v>80</v>
@@ -4242,9 +4242,9 @@
         <v>7.7424999999999997</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B294">
         <v>20</v>
@@ -4253,9 +4253,9 @@
         <v>6.1055000000000001</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B295">
         <v>28</v>
@@ -4264,9 +4264,9 @@
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B296">
         <v>29</v>
@@ -4275,9 +4275,9 @@
         <v>8.9518000000000004</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B297">
         <v>25</v>
@@ -4286,9 +4286,9 @@
         <v>11.14</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B298">
         <v>81</v>
@@ -4297,9 +4297,9 @@
         <v>6.0321999999999996</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B299">
         <v>27</v>
@@ -4308,9 +4308,9 @@
         <v>7.9112999999999998</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B300">
         <v>18</v>
@@ -4319,9 +4319,9 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B301">
         <v>79</v>
@@ -4330,9 +4330,9 @@
         <v>1.5838000000000001</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B302">
         <v>84</v>
@@ -4341,9 +4341,9 @@
         <v>6.6017000000000001</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B303">
         <v>37</v>
@@ -4352,9 +4352,9 @@
         <v>1.4422999999999999</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B304">
         <v>69</v>
@@ -4363,9 +4363,9 @@
         <v>5.3242000000000003</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B305">
         <v>8</v>
@@ -4374,9 +4374,9 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B306">
         <v>49</v>
@@ -4385,9 +4385,9 @@
         <v>0.18640000000000001</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B307">
         <v>60</v>
@@ -4396,9 +4396,9 @@
         <v>3.09E-2</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B308">
         <v>56</v>
@@ -4407,9 +4407,9 @@
         <v>0.36170000000000002</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B309">
         <v>57</v>
@@ -4418,9 +4418,9 @@
         <v>0.30120000000000002</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B310">
         <v>15</v>
@@ -4429,9 +4429,9 @@
         <v>4.2481</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B311">
         <v>65</v>
@@ -4440,9 +4440,9 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B312">
         <v>76</v>
@@ -4451,9 +4451,9 @@
         <v>5.3582999999999998</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B313">
         <v>98</v>
@@ -4462,9 +4462,9 @@
         <v>4.3700000000000003E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B314">
         <v>35</v>
@@ -4473,9 +4473,9 @@
         <v>2.214</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B315">
         <v>3</v>
@@ -4484,9 +4484,9 @@
         <v>3.4748000000000001</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B316">
         <v>86</v>
@@ -4495,9 +4495,9 @@
         <v>3.7862</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B317">
         <v>32</v>
@@ -4506,9 +4506,9 @@
         <v>4.3662000000000001</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B318">
         <v>10</v>
@@ -4517,9 +4517,9 @@
         <v>2.3818000000000001</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B319">
         <v>19</v>
@@ -4528,9 +4528,9 @@
         <v>11.66</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B320">
         <v>14</v>
@@ -4539,9 +4539,9 @@
         <v>3.9830000000000001</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B321">
         <v>97</v>
@@ -4550,9 +4550,9 @@
         <v>0.69259999999999999</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B322">
         <v>94</v>
@@ -4561,9 +4561,9 @@
         <v>4.2157</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B323">
         <v>83</v>
@@ -4572,9 +4572,9 @@
         <v>6.5015000000000001</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B324">
         <v>89</v>
@@ -4583,9 +4583,9 @@
         <v>8.2048000000000005</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B325">
         <v>42</v>
@@ -4594,9 +4594,9 @@
         <v>2.64E-2</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B326">
         <v>5</v>
@@ -4605,9 +4605,9 @@
         <v>5.9836</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B327">
         <v>77</v>
@@ -4616,9 +4616,9 @@
         <v>6.3939000000000004</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B328">
         <v>45</v>
@@ -4627,9 +4627,9 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B329">
         <v>11</v>
@@ -4638,9 +4638,9 @@
         <v>9.41</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B330">
         <v>96</v>
@@ -4649,9 +4649,9 @@
         <v>3.5160999999999998</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B331">
         <v>58</v>
@@ -4660,9 +4660,9 @@
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B332">
         <v>87</v>
@@ -4671,9 +4671,9 @@
         <v>0.67530000000000001</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B333">
         <v>59</v>
@@ -4682,9 +4682,9 @@
         <v>1.8754</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B334">
         <v>39</v>
@@ -4693,9 +4693,9 @@
         <v>3.8300000000000001E-2</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B335">
         <v>47</v>
@@ -4704,9 +4704,9 @@
         <v>0.433</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B336">
         <v>64</v>
@@ -4715,9 +4715,9 @@
         <v>0.2135</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B337">
         <v>61</v>
@@ -4726,9 +4726,9 @@
         <v>1.8835999999999999</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B338">
         <v>9</v>
@@ -4737,9 +4737,9 @@
         <v>4.5815000000000001</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B339">
         <v>48</v>
@@ -4748,9 +4748,9 @@
         <v>0.3594</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B340">
         <v>26</v>
@@ -4759,9 +4759,9 @@
         <v>2.2528999999999999</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B341">
         <v>2</v>
@@ -4770,9 +4770,9 @@
         <v>1.2948999999999999</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B342">
         <v>63</v>
@@ -4781,9 +4781,9 @@
         <v>2.52E-2</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B343">
         <v>50</v>
@@ -4792,9 +4792,9 @@
         <v>0.33629999999999999</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B344">
         <v>62</v>
@@ -4803,9 +4803,9 @@
         <v>0.43669999999999998</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B345">
         <v>40</v>
@@ -4814,9 +4814,9 @@
         <v>0.23749999999999999</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B346">
         <v>95</v>
@@ -4825,9 +4825,9 @@
         <v>3.0045000000000002</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B347">
         <v>99</v>
@@ -4836,9 +4836,9 @@
         <v>2.4428999999999998</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B348">
         <v>119</v>
@@ -4847,9 +4847,9 @@
         <v>0.14879999999999999</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B349">
         <v>6</v>
@@ -4858,9 +4858,9 @@
         <v>1.8189</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B350">
         <v>91</v>
@@ -4869,9 +4869,9 @@
         <v>7.8874000000000004</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B351">
         <v>7</v>
@@ -4880,9 +4880,9 @@
         <v>2.5173000000000001</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B352">
         <v>93</v>
@@ -4891,9 +4891,9 @@
         <v>5.2276999999999996</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B353">
         <v>1</v>
@@ -4902,9 +4902,9 @@
         <v>6.0507</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B354">
         <v>41</v>
@@ -4913,9 +4913,9 @@
         <v>0.21809999999999999</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B355">
         <v>53</v>
@@ -4924,9 +4924,9 @@
         <v>1.5102</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B356">
         <v>33</v>
@@ -4935,9 +4935,9 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B357">
         <v>54</v>
@@ -4946,9 +4946,9 @@
         <v>0.92520000000000002</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B358">
         <v>30</v>
@@ -4957,9 +4957,9 @@
         <v>3.4083000000000001</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B359">
         <v>66</v>
@@ -4968,9 +4968,9 @@
         <v>0.80169999999999997</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B360">
         <v>71</v>
@@ -4979,9 +4979,9 @@
         <v>4.1299000000000001</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B361">
         <v>72</v>
@@ -4990,9 +4990,9 @@
         <v>3.4020999999999999</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B362">
         <v>44</v>
@@ -5001,9 +5001,9 @@
         <v>0.22539999999999999</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B363">
         <v>16</v>
@@ -5012,9 +5012,9 @@
         <v>5.2858999999999998</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B364">
         <v>12</v>
@@ -5023,9 +5023,9 @@
         <v>10.43</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B365">
         <v>21</v>
@@ -5034,9 +5034,9 @@
         <v>6.944</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B366">
         <v>43</v>
@@ -5045,9 +5045,9 @@
         <v>2.5952999999999999</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B367">
         <v>55</v>
@@ -5056,9 +5056,9 @@
         <v>1.52E-2</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B368">
         <v>67</v>
@@ -5067,9 +5067,9 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B369">
         <v>52</v>
@@ -5078,9 +5078,9 @@
         <v>8.3900000000000002E-2</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B370">
         <v>17</v>
@@ -5089,9 +5089,9 @@
         <v>6.1093000000000002</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B371">
         <v>78</v>
@@ -5100,9 +5100,9 @@
         <v>3.0127999999999999</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B372">
         <v>46</v>
@@ -5111,9 +5111,9 @@
         <v>0.93589999999999995</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B373">
         <v>90</v>
@@ -5122,9 +5122,9 @@
         <v>1.7301</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B374">
         <v>82</v>
@@ -5133,9 +5133,9 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B375">
         <v>250</v>
@@ -5144,9 +5144,9 @@
         <v>7.9100000000000004E-2</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B376">
         <v>297</v>
@@ -5155,9 +5155,9 @@
         <v>5.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B377">
         <v>264</v>
@@ -5166,9 +5166,9 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B378">
         <v>38</v>
@@ -5177,9 +5177,9 @@
         <v>0.54849999999999999</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B379">
         <v>298</v>
@@ -5188,12 +5188,12 @@
         <v>7.17E-2</v>
       </c>
       <c r="D379" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B380">
         <v>24</v>
@@ -5202,9 +5202,9 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B381">
         <v>288</v>
@@ -5213,9 +5213,9 @@
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B382">
         <v>356</v>
@@ -5224,9 +5224,9 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B383">
         <v>362</v>
